--- a/data/trans_orig/P32C-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P32C-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2007</t>
+          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2007 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>921</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8237</t>
+          <t>8991</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9318</t>
+          <t>10544</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>280584</t>
+          <t>279830</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>287893</t>
+          <t>287900</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>122786</t>
+          <t>122103</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>407567</t>
+          <t>406341</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>415259</t>
+          <t>415103</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8811</t>
+          <t>8687</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>9780</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>214400</t>
+          <t>214524</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>147709</t>
+          <t>147573</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>366698</t>
+          <t>366357</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11261</t>
+          <t>11314</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11729</t>
+          <t>10545</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>327513</t>
+          <t>327460</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>336799</t>
+          <t>336784</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59867</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61774</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>388819</t>
+          <t>390003</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>398614</t>
+          <t>398601</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t>10535</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27763</t>
+          <t>28021</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7278</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11529</t>
+          <t>11022</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29514</t>
+          <t>29892</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>641776</t>
+          <t>641518</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>659675</t>
+          <t>659004</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>186111</t>
+          <t>186048</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>833351</t>
+          <t>832973</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>851336</t>
+          <t>851843</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12934</t>
+          <t>12373</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9309</t>
+          <t>9770</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16528</t>
+          <t>17803</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>203132</t>
+          <t>203693</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>213278</t>
+          <t>213287</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>131086</t>
+          <t>130625</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>339933</t>
+          <t>338658</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>352501</t>
+          <t>351866</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5578</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7130</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9118</t>
+          <t>8527</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>134210</t>
+          <t>133933</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>210970</t>
+          <t>211954</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>348493</t>
+          <t>349084</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>356602</t>
+          <t>356605</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24430</t>
+          <t>25921</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48491</t>
+          <t>50592</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>17009</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31373</t>
+          <t>32246</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58458</t>
+          <t>58847</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1827431</t>
+          <t>1825330</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1851492</t>
+          <t>1850001</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>878207</t>
+          <t>877575</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>891055</t>
+          <t>891114</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2712049</t>
+          <t>2711660</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2739134</t>
+          <t>2738261</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2012</t>
+          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2012 (tasa de respuesta: 99,17%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15226</t>
+          <t>15447</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15241</t>
+          <t>15352</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>276160</t>
+          <t>275939</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>287993</t>
+          <t>288199</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>144989</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147094</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>423239</t>
+          <t>423128</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>435500</t>
+          <t>434976</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13842</t>
+          <t>14380</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14049</t>
+          <t>14546</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>239462</t>
+          <t>238924</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>251482</t>
+          <t>252212</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>140413</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>142515</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>381770</t>
+          <t>381273</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>394022</t>
+          <t>394720</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10056</t>
+          <t>9748</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10313</t>
+          <t>10992</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>375295</t>
+          <t>375603</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>384277</t>
+          <t>384119</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75704</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77744</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>452781</t>
+          <t>452102</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>462071</t>
+          <t>462006</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21943</t>
+          <t>21910</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>5526</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8300</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23114</t>
+          <t>23342</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>635609</t>
+          <t>635642</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>649820</t>
+          <t>649675</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>223898</t>
+          <t>223283</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>863246</t>
+          <t>863018</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>878060</t>
+          <t>878291</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4788</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16076</t>
+          <t>15999</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5616</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17756</t>
+          <t>17881</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>288045</t>
+          <t>288122</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>299333</t>
+          <t>299524</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>176961</t>
+          <t>177921</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>470421</t>
+          <t>470296</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>482676</t>
+          <t>482561</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5526</t>
+          <t>6848</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5219</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>8297</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>134056</t>
+          <t>132734</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>254178</t>
+          <t>254089</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>391392</t>
+          <t>390593</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29486</t>
+          <t>29887</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>997</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31034</t>
+          <t>31239</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58411</t>
+          <t>59534</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1974146</t>
+          <t>1977183</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2001809</t>
+          <t>2001408</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1031394</t>
+          <t>1030988</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1038530</t>
+          <t>1038528</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3012409</t>
+          <t>3011286</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3039786</t>
+          <t>3039581</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2016</t>
+          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2016 (tasa de respuesta: 98,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6038,62 +6038,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2034</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6717</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>281592</t>
+          <t>281588</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>149651</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>151685</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>432668</t>
+          <t>432756</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9943</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9156</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>224331</t>
+          <t>224386</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>233216</t>
+          <t>233255</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>185967</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>188005</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>413124</t>
+          <t>412661</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>421252</t>
+          <t>421210</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11011</t>
+          <t>11505</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11328</t>
+          <t>13076</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>315830</t>
+          <t>315336</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>325725</t>
+          <t>325720</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50137</t>
+          <t>49838</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>371088</t>
+          <t>369340</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>381286</t>
+          <t>381281</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6512</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21089</t>
+          <t>22617</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6928</t>
+          <t>6430</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8351</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24609</t>
+          <t>24090</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>634301</t>
+          <t>632773</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>648878</t>
+          <t>648910</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>290649</t>
+          <t>291147</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>928357</t>
+          <t>928876</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>944615</t>
+          <t>944610</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14820</t>
+          <t>14406</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14321</t>
+          <t>14408</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>296150</t>
+          <t>296564</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>307635</t>
+          <t>307981</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>183452</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>185428</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>482077</t>
+          <t>481990</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>493232</t>
+          <t>493273</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5838</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>931</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>8718</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11125</t>
+          <t>11775</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>154109</t>
+          <t>154104</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>239557</t>
+          <t>239048</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>246846</t>
+          <t>246835</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>396588</t>
+          <t>395938</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>405792</t>
+          <t>405760</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22618</t>
+          <t>20608</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44619</t>
+          <t>43642</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13569</t>
+          <t>12663</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26733</t>
+          <t>27060</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52523</t>
+          <t>53161</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1930592</t>
+          <t>1931569</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1952593</t>
+          <t>1954603</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1112467</t>
+          <t>1113373</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1123131</t>
+          <t>1123978</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3048724</t>
+          <t>3048086</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3074514</t>
+          <t>3074187</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2023</t>
+          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2023 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8643,7 +8643,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>4803</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4291</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>493</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>278105</t>
+          <t>277753</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>158453</t>
+          <t>158254</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>439285</t>
+          <t>439280</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>444805</t>
+          <t>444807</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6283</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>171</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5739</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>206681</t>
+          <t>207277</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>212803</t>
+          <t>212794</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>132078</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>133308</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>340534</t>
+          <t>340400</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>346109</t>
+          <t>346102</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>684</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6732</t>
+          <t>6032</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>686</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6594</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>204563</t>
+          <t>205263</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>210596</t>
+          <t>210611</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39214</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>245034</t>
+          <t>245513</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>250927</t>
+          <t>250942</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>2789</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>13473</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6388</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15215</t>
+          <t>15489</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>497239</t>
+          <t>496303</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>507016</t>
+          <t>506987</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>408378</t>
+          <t>407816</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>909327</t>
+          <t>909053</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>921682</t>
+          <t>921325</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14162</t>
+          <t>13519</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>539</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>4944</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15728</t>
+          <t>15410</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>217673</t>
+          <t>218316</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>228420</t>
+          <t>228506</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>125800</t>
+          <t>126130</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>130582</t>
+          <t>130584</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>347230</t>
+          <t>347548</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>357779</t>
+          <t>358014</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -10353,97 +10353,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2228</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4530</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>11404</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>9,39%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>2228</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>11422</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>10555</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>9,41%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>2228</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>11196</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>90330</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109980</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>205066</t>
+          <t>205707</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12777</t>
+          <t>12009</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28667</t>
+          <t>27269</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16709</t>
+          <t>17382</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17539</t>
+          <t>17638</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39431</t>
+          <t>38596</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1514619</t>
+          <t>1516017</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1530509</t>
+          <t>1531277</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>986967</t>
+          <t>986294</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1000615</t>
+          <t>1000664</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2507531</t>
+          <t>2508366</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2529423</t>
+          <t>2529324</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">

--- a/data/trans_orig/P32C-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P32C-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>906</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8991</t>
+          <t>8572</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>1761</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10544</t>
+          <t>10541</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>279830</t>
+          <t>280249</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>287900</t>
+          <t>287915</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>122103</t>
+          <t>122948</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>406341</t>
+          <t>406344</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>415103</t>
+          <t>415124</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8687</t>
+          <t>9334</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>5632</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9780</t>
+          <t>10424</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>214524</t>
+          <t>213877</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>147573</t>
+          <t>147294</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>366357</t>
+          <t>365713</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11314</t>
+          <t>10991</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10545</t>
+          <t>10979</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>327460</t>
+          <t>327783</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>336784</t>
+          <t>336875</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>390003</t>
+          <t>389569</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>398601</t>
+          <t>398212</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10535</t>
+          <t>10010</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28021</t>
+          <t>27821</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11022</t>
+          <t>10788</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29892</t>
+          <t>28870</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>641518</t>
+          <t>641718</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>659004</t>
+          <t>659529</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>186048</t>
+          <t>186011</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>832973</t>
+          <t>833995</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>851843</t>
+          <t>852077</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2779</t>
+          <t>2846</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12373</t>
+          <t>13627</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>9635</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17803</t>
+          <t>17506</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>203693</t>
+          <t>202439</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>213287</t>
+          <t>213220</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>130625</t>
+          <t>130760</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>338658</t>
+          <t>338955</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>351866</t>
+          <t>351686</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5578</t>
+          <t>5868</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8527</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>133933</t>
+          <t>133643</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>211954</t>
+          <t>211019</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>349084</t>
+          <t>349338</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>356605</t>
+          <t>356603</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25921</t>
+          <t>25226</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50592</t>
+          <t>48493</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17009</t>
+          <t>16168</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32246</t>
+          <t>30650</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58847</t>
+          <t>59366</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1825330</t>
+          <t>1827429</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1850001</t>
+          <t>1850696</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>877575</t>
+          <t>878416</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>891114</t>
+          <t>890882</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2711660</t>
+          <t>2711141</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2738261</t>
+          <t>2739857</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>3516</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15447</t>
+          <t>16446</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>2984</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15352</t>
+          <t>15678</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>275939</t>
+          <t>274940</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288199</t>
+          <t>287870</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>423128</t>
+          <t>422802</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>434976</t>
+          <t>435496</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14380</t>
+          <t>13274</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14546</t>
+          <t>15963</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>238924</t>
+          <t>240030</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>252212</t>
+          <t>252242</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>381273</t>
+          <t>379856</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>394720</t>
+          <t>394002</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9748</t>
+          <t>10669</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10992</t>
+          <t>10026</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>375603</t>
+          <t>374682</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>384119</t>
+          <t>384235</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>452102</t>
+          <t>453068</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>462006</t>
+          <t>462008</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7877</t>
+          <t>7581</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21910</t>
+          <t>22946</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5526</t>
+          <t>5052</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23342</t>
+          <t>22990</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>635642</t>
+          <t>634606</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>649675</t>
+          <t>649971</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>223283</t>
+          <t>223757</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>863018</t>
+          <t>863370</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>878291</t>
+          <t>878194</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4597</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15999</t>
+          <t>15817</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>5362</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17881</t>
+          <t>18086</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>288122</t>
+          <t>288304</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>299524</t>
+          <t>299462</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>177921</t>
+          <t>179612</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>470296</t>
+          <t>470091</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>482561</t>
+          <t>482815</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8297</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>132734</t>
+          <t>134254</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>254089</t>
+          <t>254115</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>390593</t>
+          <t>390498</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29887</t>
+          <t>29692</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54112</t>
+          <t>57119</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8537</t>
+          <t>8126</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31239</t>
+          <t>32459</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>59534</t>
+          <t>59162</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1977183</t>
+          <t>1974176</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2001408</t>
+          <t>2001603</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1030988</t>
+          <t>1031399</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1038528</t>
+          <t>1039525</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3011286</t>
+          <t>3011658</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3039581</t>
+          <t>3038361</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>5918</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6717</t>
+          <t>6737</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>281588</t>
+          <t>281871</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>432756</t>
+          <t>432736</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9888</t>
+          <t>9455</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9619</t>
+          <t>10989</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>224386</t>
+          <t>224819</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>233255</t>
+          <t>233227</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>412661</t>
+          <t>411291</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>421210</t>
+          <t>421165</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11505</t>
+          <t>10438</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13076</t>
+          <t>12110</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>315336</t>
+          <t>316403</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>325720</t>
+          <t>325726</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49838</t>
+          <t>49459</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>369340</t>
+          <t>370306</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>381281</t>
+          <t>381287</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6480</t>
+          <t>7111</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22617</t>
+          <t>22328</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6430</t>
+          <t>7354</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8356</t>
+          <t>8413</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24090</t>
+          <t>23248</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>632773</t>
+          <t>633062</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>648910</t>
+          <t>648279</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>291147</t>
+          <t>290223</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>928876</t>
+          <t>929718</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>944610</t>
+          <t>944553</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14406</t>
+          <t>14112</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14408</t>
+          <t>15076</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>296564</t>
+          <t>296858</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>307981</t>
+          <t>307851</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>481990</t>
+          <t>481322</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>493273</t>
+          <t>493261</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>6755</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>918</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8718</t>
+          <t>9249</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11775</t>
+          <t>11611</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>154104</t>
+          <t>153192</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>239048</t>
+          <t>238517</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>246835</t>
+          <t>246848</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>395938</t>
+          <t>396102</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>405760</t>
+          <t>405797</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20608</t>
+          <t>21650</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43642</t>
+          <t>45180</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12663</t>
+          <t>12945</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27060</t>
+          <t>26821</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53161</t>
+          <t>52759</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1931569</t>
+          <t>1930031</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1954603</t>
+          <t>1953561</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1113373</t>
+          <t>1113091</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1123978</t>
+          <t>1124007</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3048086</t>
+          <t>3048488</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3074187</t>
+          <t>3074426</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>868</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,22 +8703,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>540</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -8746,27 +8746,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>281673</t>
+          <t>302669</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>277753</t>
+          <t>299260</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>282556</t>
+          <t>303537</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -8781,27 +8781,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>161433</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>158254</t>
+          <t>170688</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>162744</t>
+          <t>175414</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8816,27 +8816,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>443105</t>
+          <t>476720</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>439280</t>
+          <t>473002</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>444807</t>
+          <t>478410</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>282556</t>
+          <t>303537</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>282556</t>
+          <t>303537</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>282556</t>
+          <t>303537</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>162744</t>
+          <t>175414</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>162744</t>
+          <t>175414</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>162744</t>
+          <t>175414</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>445300</t>
+          <t>478950</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>445300</t>
+          <t>478950</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>445300</t>
+          <t>478950</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>701</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5687</t>
+          <t>6986</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>703</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>211114</t>
+          <t>222126</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>207277</t>
+          <t>217705</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>212794</t>
+          <t>223990</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>133308</t>
+          <t>145015</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>344423</t>
+          <t>367141</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>340400</t>
+          <t>362398</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>346102</t>
+          <t>369003</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>212964</t>
+          <t>224691</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>212964</t>
+          <t>224691</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>212964</t>
+          <t>224691</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>133308</t>
+          <t>145015</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>133308</t>
+          <t>145015</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>133308</t>
+          <t>145015</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>346273</t>
+          <t>369706</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>346273</t>
+          <t>369706</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>346273</t>
+          <t>369706</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>773</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6032</t>
+          <t>6993</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>788</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>208847</t>
+          <t>225642</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>205263</t>
+          <t>221116</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>210611</t>
+          <t>227336</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>249180</t>
+          <t>272207</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>245513</t>
+          <t>268174</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>250942</t>
+          <t>273886</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>211295</t>
+          <t>228109</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>211295</t>
+          <t>228109</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>211295</t>
+          <t>228109</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>251628</t>
+          <t>274674</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>251628</t>
+          <t>274674</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>251628</t>
+          <t>274674</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>6684</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2789</t>
+          <t>3083</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13473</t>
+          <t>13753</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>862</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6950</t>
+          <t>13005</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>8442</t>
+          <t>10851</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15489</t>
+          <t>19658</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>503360</t>
+          <t>536207</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>496303</t>
+          <t>529138</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>506987</t>
+          <t>539808</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>412740</t>
+          <t>226272</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>407816</t>
+          <t>217434</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>414766</t>
+          <t>229577</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>916100</t>
+          <t>762479</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>909053</t>
+          <t>753672</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>921325</t>
+          <t>767712</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>509776</t>
+          <t>542891</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>509776</t>
+          <t>542891</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>509776</t>
+          <t>542891</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>414766</t>
+          <t>230439</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>414766</t>
+          <t>230439</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>414766</t>
+          <t>230439</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>924542</t>
+          <t>773330</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>924542</t>
+          <t>773330</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>924542</t>
+          <t>773330</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7219</t>
+          <t>7299</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3329</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13519</t>
+          <t>14194</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>691</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>9297</t>
+          <t>9473</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4944</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15410</t>
+          <t>15820</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>224616</t>
+          <t>250478</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>218316</t>
+          <t>243583</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>228506</t>
+          <t>254212</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>129045</t>
+          <t>151074</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>126130</t>
+          <t>147720</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>130584</t>
+          <t>152557</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>353661</t>
+          <t>401552</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>347548</t>
+          <t>395205</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>358014</t>
+          <t>405789</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>231835</t>
+          <t>257777</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>231835</t>
+          <t>257777</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>231835</t>
+          <t>257777</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>131123</t>
+          <t>153248</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>131123</t>
+          <t>153248</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>131123</t>
+          <t>153248</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>362958</t>
+          <t>411025</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>362958</t>
+          <t>411025</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>362958</t>
+          <t>411025</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11404</t>
+          <t>11629</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,7 +10418,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -10428,12 +10428,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10555</t>
+          <t>11279</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -10461,7 +10461,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>85841</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -10496,27 +10496,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>119174</t>
+          <t>124247</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>114842</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>121402</t>
+          <t>126471</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10531,27 +10531,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>214034</t>
+          <t>210088</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>205707</t>
+          <t>201033</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>216262</t>
+          <t>212312</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>85841</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>85841</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>85841</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>121402</t>
+          <t>126471</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>121402</t>
+          <t>126471</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>121402</t>
+          <t>126471</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>216262</t>
+          <t>212312</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>216262</t>
+          <t>212312</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>216262</t>
+          <t>212312</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>18817</t>
+          <t>19884</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12009</t>
+          <t>13056</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27269</t>
+          <t>29451</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>9926</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3012</t>
+          <t>5093</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17382</t>
+          <t>22669</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>26459</t>
+          <t>29810</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17638</t>
+          <t>20344</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38596</t>
+          <t>42542</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1524469</t>
+          <t>1622962</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1516017</t>
+          <t>1613395</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1531277</t>
+          <t>1629790</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>996034</t>
+          <t>867225</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>986294</t>
+          <t>854482</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1000664</t>
+          <t>872058</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2520503</t>
+          <t>2490187</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2508366</t>
+          <t>2477455</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2529324</t>
+          <t>2499653</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1543286</t>
+          <t>1642846</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1543286</t>
+          <t>1642846</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1543286</t>
+          <t>1642846</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1003676</t>
+          <t>877151</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1003676</t>
+          <t>877151</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1003676</t>
+          <t>877151</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2546962</t>
+          <t>2519997</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2546962</t>
+          <t>2519997</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2546962</t>
+          <t>2519997</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
